--- a/spc_excel/SPC_기록템플릿.xlsx
+++ b/spc_excel/SPC_기록템플릿.xlsx
@@ -6483,39 +6483,14 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="A13:B15"/>
   </mergeCells>
+  <conditionalFormatting sqref="G7:AE26">
+    <cfRule type="expression" priority="1" dxfId="11">
+      <formula>AND(ISNUMBER(G7),ISNUMBER($C$21),OR(AND(ISNUMBER($C$25),G7&lt;$C$21-$C$25),AND(ISNUMBER($C$23),G7&gt;$C$21+$C$23)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C32">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="11">
       <formula>0.33</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G26 I7:I26 K7:L26 P7:X26 Z7:Z26 AB7:AE26">
-    <cfRule type="cellIs" priority="6" operator="notBetween" dxfId="11">
-      <formula>3495</formula>
-      <formula>3637</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H26">
-    <cfRule type="cellIs" priority="1" operator="notBetween" dxfId="11">
-      <formula>$C$37</formula>
-      <formula>$C$38</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J26">
-    <cfRule type="cellIs" priority="3" operator="notBetween" dxfId="11">
-      <formula>$C$37</formula>
-      <formula>$C$38</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y26">
-    <cfRule type="cellIs" priority="2" operator="notBetween" dxfId="9" stopIfTrue="1">
-      <formula>$D$9</formula>
-      <formula>$F$9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA26">
-    <cfRule type="cellIs" priority="4" operator="notBetween" dxfId="9" stopIfTrue="1">
-      <formula>$D$9</formula>
-      <formula>$F$9</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
